--- a/hisobotlar/tekshiruvlar/SHUBHALI_MALUMOTLAR_HISOBOTI.xlsx
+++ b/hisobotlar/tekshiruvlar/SHUBHALI_MALUMOTLAR_HISOBOTI.xlsx
@@ -16,12 +16,12 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tasdiqlangan istisnolar" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Shubhali ma''lumotlar'!$A$1:$J$59</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Talabalar kesimida'!$A$1:$G$41</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Shubhali ma''lumotlar'!$A$1:$J$49</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Talabalar kesimida'!$A$1:$G$33</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Bugungi o''zgarishlar'!$A$1:$G$190</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Chiqarilganlar'!$A$1:$D$4</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Telefonlar manbasi'!$A$1:$E$176</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Tasdiqlangan istisnolar'!$A$1:$F$2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Tasdiqlangan istisnolar'!$A$1:$F$3</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -595,7 +595,7 @@
         </is>
       </c>
       <c r="B5" s="4">
-        <f>COUNTA('Talabalar kesimida'!$D$2:$D$41)</f>
+        <f>COUNTA('Talabalar kesimida'!$D$2:$D$33)</f>
         <v/>
       </c>
     </row>
@@ -606,7 +606,7 @@
         </is>
       </c>
       <c r="B6" s="4">
-        <f>COUNTA('Shubhali ma''lumotlar'!$A$2:$A$59)</f>
+        <f>COUNTA('Shubhali ma''lumotlar'!$A$2:$A$49)</f>
         <v/>
       </c>
     </row>
@@ -670,27 +670,27 @@
         </is>
       </c>
       <c r="B10" s="7">
-        <f>SUMPRODUCT(('Shubhali ma''lumotlar'!$B$2:$B$59=$A10)*('Shubhali ma''lumotlar'!$C$2:$C$59=B$9))</f>
+        <f>SUMPRODUCT(('Shubhali ma''lumotlar'!$B$2:$B$49=$A10)*('Shubhali ma''lumotlar'!$C$2:$C$49=B$9))</f>
         <v/>
       </c>
       <c r="C10" s="7">
-        <f>SUMPRODUCT(('Shubhali ma''lumotlar'!$B$2:$B$59=$A10)*('Shubhali ma''lumotlar'!$C$2:$C$59=C$9))</f>
+        <f>SUMPRODUCT(('Shubhali ma''lumotlar'!$B$2:$B$49=$A10)*('Shubhali ma''lumotlar'!$C$2:$C$49=C$9))</f>
         <v/>
       </c>
       <c r="D10" s="7">
-        <f>SUMPRODUCT(('Shubhali ma''lumotlar'!$B$2:$B$59=$A10)*('Shubhali ma''lumotlar'!$C$2:$C$59=D$9))</f>
+        <f>SUMPRODUCT(('Shubhali ma''lumotlar'!$B$2:$B$49=$A10)*('Shubhali ma''lumotlar'!$C$2:$C$49=D$9))</f>
         <v/>
       </c>
       <c r="E10" s="7">
-        <f>SUMPRODUCT(('Shubhali ma''lumotlar'!$B$2:$B$59=$A10)*('Shubhali ma''lumotlar'!$C$2:$C$59=E$9))</f>
+        <f>SUMPRODUCT(('Shubhali ma''lumotlar'!$B$2:$B$49=$A10)*('Shubhali ma''lumotlar'!$C$2:$C$49=E$9))</f>
         <v/>
       </c>
       <c r="F10" s="7">
-        <f>SUMPRODUCT(('Shubhali ma''lumotlar'!$B$2:$B$59=$A10)*('Shubhali ma''lumotlar'!$C$2:$C$59=F$9))</f>
+        <f>SUMPRODUCT(('Shubhali ma''lumotlar'!$B$2:$B$49=$A10)*('Shubhali ma''lumotlar'!$C$2:$C$49=F$9))</f>
         <v/>
       </c>
       <c r="G10" s="7">
-        <f>SUMPRODUCT(('Shubhali ma''lumotlar'!$B$2:$B$59=$A10)*('Shubhali ma''lumotlar'!$C$2:$C$59=G$9))</f>
+        <f>SUMPRODUCT(('Shubhali ma''lumotlar'!$B$2:$B$49=$A10)*('Shubhali ma''lumotlar'!$C$2:$C$49=G$9))</f>
         <v/>
       </c>
       <c r="H10" s="8">
@@ -705,27 +705,27 @@
         </is>
       </c>
       <c r="B11" s="7">
-        <f>SUMPRODUCT(('Shubhali ma''lumotlar'!$B$2:$B$59=$A11)*('Shubhali ma''lumotlar'!$C$2:$C$59=B$9))</f>
+        <f>SUMPRODUCT(('Shubhali ma''lumotlar'!$B$2:$B$49=$A11)*('Shubhali ma''lumotlar'!$C$2:$C$49=B$9))</f>
         <v/>
       </c>
       <c r="C11" s="7">
-        <f>SUMPRODUCT(('Shubhali ma''lumotlar'!$B$2:$B$59=$A11)*('Shubhali ma''lumotlar'!$C$2:$C$59=C$9))</f>
+        <f>SUMPRODUCT(('Shubhali ma''lumotlar'!$B$2:$B$49=$A11)*('Shubhali ma''lumotlar'!$C$2:$C$49=C$9))</f>
         <v/>
       </c>
       <c r="D11" s="7">
-        <f>SUMPRODUCT(('Shubhali ma''lumotlar'!$B$2:$B$59=$A11)*('Shubhali ma''lumotlar'!$C$2:$C$59=D$9))</f>
+        <f>SUMPRODUCT(('Shubhali ma''lumotlar'!$B$2:$B$49=$A11)*('Shubhali ma''lumotlar'!$C$2:$C$49=D$9))</f>
         <v/>
       </c>
       <c r="E11" s="7">
-        <f>SUMPRODUCT(('Shubhali ma''lumotlar'!$B$2:$B$59=$A11)*('Shubhali ma''lumotlar'!$C$2:$C$59=E$9))</f>
+        <f>SUMPRODUCT(('Shubhali ma''lumotlar'!$B$2:$B$49=$A11)*('Shubhali ma''lumotlar'!$C$2:$C$49=E$9))</f>
         <v/>
       </c>
       <c r="F11" s="7">
-        <f>SUMPRODUCT(('Shubhali ma''lumotlar'!$B$2:$B$59=$A11)*('Shubhali ma''lumotlar'!$C$2:$C$59=F$9))</f>
+        <f>SUMPRODUCT(('Shubhali ma''lumotlar'!$B$2:$B$49=$A11)*('Shubhali ma''lumotlar'!$C$2:$C$49=F$9))</f>
         <v/>
       </c>
       <c r="G11" s="7">
-        <f>SUMPRODUCT(('Shubhali ma''lumotlar'!$B$2:$B$59=$A11)*('Shubhali ma''lumotlar'!$C$2:$C$59=G$9))</f>
+        <f>SUMPRODUCT(('Shubhali ma''lumotlar'!$B$2:$B$49=$A11)*('Shubhali ma''lumotlar'!$C$2:$C$49=G$9))</f>
         <v/>
       </c>
       <c r="H11" s="8">
@@ -740,27 +740,27 @@
         </is>
       </c>
       <c r="B12" s="7">
-        <f>SUMPRODUCT(('Shubhali ma''lumotlar'!$B$2:$B$59=$A12)*('Shubhali ma''lumotlar'!$C$2:$C$59=B$9))</f>
+        <f>SUMPRODUCT(('Shubhali ma''lumotlar'!$B$2:$B$49=$A12)*('Shubhali ma''lumotlar'!$C$2:$C$49=B$9))</f>
         <v/>
       </c>
       <c r="C12" s="7">
-        <f>SUMPRODUCT(('Shubhali ma''lumotlar'!$B$2:$B$59=$A12)*('Shubhali ma''lumotlar'!$C$2:$C$59=C$9))</f>
+        <f>SUMPRODUCT(('Shubhali ma''lumotlar'!$B$2:$B$49=$A12)*('Shubhali ma''lumotlar'!$C$2:$C$49=C$9))</f>
         <v/>
       </c>
       <c r="D12" s="7">
-        <f>SUMPRODUCT(('Shubhali ma''lumotlar'!$B$2:$B$59=$A12)*('Shubhali ma''lumotlar'!$C$2:$C$59=D$9))</f>
+        <f>SUMPRODUCT(('Shubhali ma''lumotlar'!$B$2:$B$49=$A12)*('Shubhali ma''lumotlar'!$C$2:$C$49=D$9))</f>
         <v/>
       </c>
       <c r="E12" s="7">
-        <f>SUMPRODUCT(('Shubhali ma''lumotlar'!$B$2:$B$59=$A12)*('Shubhali ma''lumotlar'!$C$2:$C$59=E$9))</f>
+        <f>SUMPRODUCT(('Shubhali ma''lumotlar'!$B$2:$B$49=$A12)*('Shubhali ma''lumotlar'!$C$2:$C$49=E$9))</f>
         <v/>
       </c>
       <c r="F12" s="7">
-        <f>SUMPRODUCT(('Shubhali ma''lumotlar'!$B$2:$B$59=$A12)*('Shubhali ma''lumotlar'!$C$2:$C$59=F$9))</f>
+        <f>SUMPRODUCT(('Shubhali ma''lumotlar'!$B$2:$B$49=$A12)*('Shubhali ma''lumotlar'!$C$2:$C$49=F$9))</f>
         <v/>
       </c>
       <c r="G12" s="7">
-        <f>SUMPRODUCT(('Shubhali ma''lumotlar'!$B$2:$B$59=$A12)*('Shubhali ma''lumotlar'!$C$2:$C$59=G$9))</f>
+        <f>SUMPRODUCT(('Shubhali ma''lumotlar'!$B$2:$B$49=$A12)*('Shubhali ma''lumotlar'!$C$2:$C$49=G$9))</f>
         <v/>
       </c>
       <c r="H12" s="8">
@@ -834,7 +834,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J59"/>
+  <dimension ref="A1:J49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -1742,7 +1742,7 @@
       </c>
       <c r="G19" s="17" t="inlineStr">
         <is>
-          <t>916397685</t>
+          <t>908785105</t>
         </is>
       </c>
       <c r="H19" s="17" t="inlineStr">
@@ -1792,7 +1792,7 @@
       </c>
       <c r="G20" s="17" t="inlineStr">
         <is>
-          <t>908785105</t>
+          <t>916397685</t>
         </is>
       </c>
       <c r="H20" s="17" t="inlineStr">
@@ -1877,32 +1877,32 @@
       </c>
       <c r="D22" s="17" t="inlineStr">
         <is>
-          <t>Eshnazarova Dilnoza Rustam qizi</t>
+          <t>Izzatulloyeva Vazira G'ayratzoda</t>
         </is>
       </c>
       <c r="E22" s="17" t="inlineStr">
         <is>
-          <t>221</t>
+          <t>383</t>
         </is>
       </c>
       <c r="F22" s="17" t="inlineStr">
         <is>
-          <t>Yashash viloyat+tumani</t>
+          <t>Otasining ismi</t>
         </is>
       </c>
       <c r="G22" s="17" t="inlineStr">
         <is>
-          <t>PINFL hudud kodi 573</t>
+          <t>G'ayratzoda</t>
         </is>
       </c>
       <c r="H22" s="17" t="inlineStr">
         <is>
-          <t>Yashash hududi aniqlanmadi (muassasa nomida tuman yo'q, PINFL hudud kodi noma'lum)</t>
+          <t>Otasining ismi 'qizi / o'g'li' bilan tugamagan</t>
         </is>
       </c>
       <c r="I22" s="17" t="inlineStr">
         <is>
-          <t>Shablonda bo'sh qoldirildi — qo'lda kiriting</t>
+          <t>Pasport bilan solishtiring</t>
         </is>
       </c>
       <c r="J22" s="17" t="inlineStr">
@@ -1927,32 +1927,32 @@
       </c>
       <c r="D23" s="17" t="inlineStr">
         <is>
-          <t>Fayzullayeva Sarvinoz Sherbobo qizi</t>
+          <t>Izzatulloyeva Vazira G'ayratzoda</t>
         </is>
       </c>
       <c r="E23" s="17" t="inlineStr">
         <is>
-          <t>152</t>
+          <t>383</t>
         </is>
       </c>
       <c r="F23" s="17" t="inlineStr">
         <is>
-          <t>Yashash viloyat+tumani</t>
+          <t>Tasdiq</t>
         </is>
       </c>
       <c r="G23" s="17" t="inlineStr">
         <is>
-          <t>PINFL hudud kodi 573</t>
+          <t>KUTILMOQDA</t>
         </is>
       </c>
       <c r="H23" s="17" t="inlineStr">
         <is>
-          <t>Yashash hududi aniqlanmadi (muassasa nomida tuman yo'q, PINFL hudud kodi noma'lum)</t>
+          <t>Ma'lumotlar hali hujjat bilan tasdiqlanmagan</t>
         </is>
       </c>
       <c r="I23" s="17" t="inlineStr">
         <is>
-          <t>Shablonda bo'sh qoldirildi — qo'lda kiriting</t>
+          <t>Hujjat nusxasi bilan solishtirib tasdiqlang</t>
         </is>
       </c>
       <c r="J23" s="17" t="inlineStr">
@@ -1977,39 +1977,31 @@
       </c>
       <c r="D24" s="17" t="inlineStr">
         <is>
-          <t>Izzatulloyeva Vazira G'ayratzoda</t>
-        </is>
-      </c>
-      <c r="E24" s="17" t="inlineStr">
-        <is>
-          <t>383</t>
-        </is>
-      </c>
+          <t>Niyozova Komila Toshpulatovna</t>
+        </is>
+      </c>
+      <c r="E24" s="17" t="inlineStr"/>
       <c r="F24" s="17" t="inlineStr">
         <is>
-          <t>Otasining ismi</t>
+          <t>Tasdiq</t>
         </is>
       </c>
       <c r="G24" s="17" t="inlineStr">
         <is>
-          <t>G'ayratzoda</t>
+          <t>KUTILMOQDA</t>
         </is>
       </c>
       <c r="H24" s="17" t="inlineStr">
         <is>
-          <t>Otasining ismi 'qizi / o'g'li' bilan tugamagan</t>
+          <t>Ma'lumotlar hali hujjat bilan tasdiqlanmagan</t>
         </is>
       </c>
       <c r="I24" s="17" t="inlineStr">
         <is>
-          <t>Pasport bilan solishtiring</t>
-        </is>
-      </c>
-      <c r="J24" s="17" t="inlineStr">
-        <is>
-          <t>Ha</t>
-        </is>
-      </c>
+          <t>Hujjat nusxasi bilan solishtirib tasdiqlang</t>
+        </is>
+      </c>
+      <c r="J24" s="17" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="17" t="n">
@@ -2027,32 +2019,32 @@
       </c>
       <c r="D25" s="17" t="inlineStr">
         <is>
-          <t>Izzatulloyeva Vazira G'ayratzoda</t>
+          <t>Primova Husnora Shovkat qizi</t>
         </is>
       </c>
       <c r="E25" s="17" t="inlineStr">
         <is>
-          <t>383</t>
+          <t>251</t>
         </is>
       </c>
       <c r="F25" s="17" t="inlineStr">
         <is>
-          <t>Tasdiq</t>
+          <t>Pasport</t>
         </is>
       </c>
       <c r="G25" s="17" t="inlineStr">
         <is>
-          <t>KUTILMOQDA</t>
+          <t>AC 0443770</t>
         </is>
       </c>
       <c r="H25" s="17" t="inlineStr">
         <is>
-          <t>Ma'lumotlar hali hujjat bilan tasdiqlanmagan</t>
+          <t>Pasport raqamida bo'shliq / kichik harf bor</t>
         </is>
       </c>
       <c r="I25" s="17" t="inlineStr">
         <is>
-          <t>Hujjat nusxasi bilan solishtirib tasdiqlang</t>
+          <t>To'g'ri yozilishi: AC0443770 (shablonda tozalandi)</t>
         </is>
       </c>
       <c r="J25" s="17" t="inlineStr">
@@ -2077,10 +2069,14 @@
       </c>
       <c r="D26" s="17" t="inlineStr">
         <is>
-          <t>Niyozova Komila Toshpulatovna</t>
-        </is>
-      </c>
-      <c r="E26" s="17" t="inlineStr"/>
+          <t>Salayeva Dilroz Muroulla qizi</t>
+        </is>
+      </c>
+      <c r="E26" s="17" t="inlineStr">
+        <is>
+          <t>205</t>
+        </is>
+      </c>
       <c r="F26" s="17" t="inlineStr">
         <is>
           <t>Tasdiq</t>
@@ -2101,7 +2097,11 @@
           <t>Hujjat nusxasi bilan solishtirib tasdiqlang</t>
         </is>
       </c>
-      <c r="J26" s="17" t="inlineStr"/>
+      <c r="J26" s="17" t="inlineStr">
+        <is>
+          <t>Ha</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="17" t="n">
@@ -2119,32 +2119,32 @@
       </c>
       <c r="D27" s="17" t="inlineStr">
         <is>
-          <t>Primova Husnora Shovkat qizi</t>
+          <t>Xolmamatova Shoxista Sobir qizi</t>
         </is>
       </c>
       <c r="E27" s="17" t="inlineStr">
         <is>
-          <t>251</t>
+          <t>243</t>
         </is>
       </c>
       <c r="F27" s="17" t="inlineStr">
         <is>
-          <t>Pasport</t>
+          <t>Telefon</t>
         </is>
       </c>
       <c r="G27" s="17" t="inlineStr">
         <is>
-          <t>AC 0443770</t>
+          <t>908785105</t>
         </is>
       </c>
       <c r="H27" s="17" t="inlineStr">
         <is>
-          <t>Pasport raqamida bo'shliq / kichik harf bor</t>
+          <t>Bir xil telefon raqami: Quysinova Rohshona To'lqin qizi, Xolmamatova Shoxista Sobir qizi, Zayidova Shaboda Sodiqovna</t>
         </is>
       </c>
       <c r="I27" s="17" t="inlineStr">
         <is>
-          <t>To'g'ri yozilishi: AC0443770 (shablonda tozalandi)</t>
+          <t>Aka-uka/opa-singil bo'lishi mumkin — tekshiring</t>
         </is>
       </c>
       <c r="J27" s="17" t="inlineStr">
@@ -2169,32 +2169,32 @@
       </c>
       <c r="D28" s="17" t="inlineStr">
         <is>
-          <t>Salayeva Dilroz Muroulla qizi</t>
+          <t>Xolmamatova Shoxista Sobir qizi</t>
         </is>
       </c>
       <c r="E28" s="17" t="inlineStr">
         <is>
-          <t>205</t>
+          <t>243</t>
         </is>
       </c>
       <c r="F28" s="17" t="inlineStr">
         <is>
-          <t>Yashash viloyat+tumani</t>
+          <t>Telefon</t>
         </is>
       </c>
       <c r="G28" s="17" t="inlineStr">
         <is>
-          <t>PINFL hudud kodi 573</t>
+          <t>916397685</t>
         </is>
       </c>
       <c r="H28" s="17" t="inlineStr">
         <is>
-          <t>Yashash hududi aniqlanmadi (muassasa nomida tuman yo'q, PINFL hudud kodi noma'lum)</t>
+          <t>Bir xil telefon raqami: Quysinova Rohshona To'lqin qizi, Xolmamatova Shoxista Sobir qizi, Zayidova Shaboda Sodiqovna</t>
         </is>
       </c>
       <c r="I28" s="17" t="inlineStr">
         <is>
-          <t>Shablonda bo'sh qoldirildi — qo'lda kiriting</t>
+          <t>Aka-uka/opa-singil bo'lishi mumkin — tekshiring</t>
         </is>
       </c>
       <c r="J28" s="17" t="inlineStr">
@@ -2219,12 +2219,12 @@
       </c>
       <c r="D29" s="17" t="inlineStr">
         <is>
-          <t>Salayeva Dilroz Muroulla qizi</t>
+          <t>Xurramova Sabina Yuldosh qizi</t>
         </is>
       </c>
       <c r="E29" s="17" t="inlineStr">
         <is>
-          <t>205</t>
+          <t>52</t>
         </is>
       </c>
       <c r="F29" s="17" t="inlineStr">
@@ -2264,44 +2264,40 @@
       </c>
       <c r="C30" s="17" t="inlineStr">
         <is>
-          <t>26-03</t>
+          <t>26-04</t>
         </is>
       </c>
       <c r="D30" s="17" t="inlineStr">
         <is>
-          <t>Shamsiyeva Fotima Sharofiddin qizi</t>
+          <t>Jalolov Javlonbek G'ani o'g'li</t>
         </is>
       </c>
       <c r="E30" s="17" t="inlineStr">
         <is>
-          <t>107</t>
+          <t>211</t>
         </is>
       </c>
       <c r="F30" s="17" t="inlineStr">
         <is>
-          <t>Yashash viloyat+tumani</t>
+          <t>Pasport</t>
         </is>
       </c>
       <c r="G30" s="17" t="inlineStr">
         <is>
-          <t>PINFL hudud kodi 573</t>
+          <t>AE 4994200</t>
         </is>
       </c>
       <c r="H30" s="17" t="inlineStr">
         <is>
-          <t>Yashash hududi aniqlanmadi (muassasa nomida tuman yo'q, PINFL hudud kodi noma'lum)</t>
+          <t>Pasport raqamida bo'shliq / kichik harf bor</t>
         </is>
       </c>
       <c r="I30" s="17" t="inlineStr">
         <is>
-          <t>Shablonda bo'sh qoldirildi — qo'lda kiriting</t>
-        </is>
-      </c>
-      <c r="J30" s="17" t="inlineStr">
-        <is>
-          <t>Ha</t>
-        </is>
-      </c>
+          <t>To'g'ri yozilishi: AE4994200 (shablonda tozalandi)</t>
+        </is>
+      </c>
+      <c r="J30" s="17" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="17" t="n">
@@ -2314,37 +2310,37 @@
       </c>
       <c r="C31" s="17" t="inlineStr">
         <is>
-          <t>26-03</t>
+          <t>26-04</t>
         </is>
       </c>
       <c r="D31" s="17" t="inlineStr">
         <is>
-          <t>Xolmamatova Shoxista Sobir qizi</t>
+          <t>Ulugbekova Zara Ulug'bek qizi</t>
         </is>
       </c>
       <c r="E31" s="17" t="inlineStr">
         <is>
-          <t>243</t>
+          <t>313</t>
         </is>
       </c>
       <c r="F31" s="17" t="inlineStr">
         <is>
-          <t>Telefon</t>
+          <t>Tasdiq</t>
         </is>
       </c>
       <c r="G31" s="17" t="inlineStr">
         <is>
-          <t>916397685</t>
+          <t>KUTILMOQDA</t>
         </is>
       </c>
       <c r="H31" s="17" t="inlineStr">
         <is>
-          <t>Bir xil telefon raqami: Quysinova Rohshona To'lqin qizi, Xolmamatova Shoxista Sobir qizi, Zayidova Shaboda Sodiqovna</t>
+          <t>Ma'lumotlar hali hujjat bilan tasdiqlanmagan</t>
         </is>
       </c>
       <c r="I31" s="17" t="inlineStr">
         <is>
-          <t>Aka-uka/opa-singil bo'lishi mumkin — tekshiring</t>
+          <t>Hujjat nusxasi bilan solishtirib tasdiqlang</t>
         </is>
       </c>
       <c r="J31" s="17" t="inlineStr">
@@ -2364,37 +2360,37 @@
       </c>
       <c r="C32" s="17" t="inlineStr">
         <is>
-          <t>26-03</t>
+          <t>26-04</t>
         </is>
       </c>
       <c r="D32" s="17" t="inlineStr">
         <is>
-          <t>Xolmamatova Shoxista Sobir qizi</t>
+          <t>Xujamuratova Durdona Bahrom qizi</t>
         </is>
       </c>
       <c r="E32" s="17" t="inlineStr">
         <is>
-          <t>243</t>
+          <t>232</t>
         </is>
       </c>
       <c r="F32" s="17" t="inlineStr">
         <is>
-          <t>Telefon</t>
+          <t>Tasdiq</t>
         </is>
       </c>
       <c r="G32" s="17" t="inlineStr">
         <is>
-          <t>908785105</t>
+          <t>KUTILMOQDA</t>
         </is>
       </c>
       <c r="H32" s="17" t="inlineStr">
         <is>
-          <t>Bir xil telefon raqami: Quysinova Rohshona To'lqin qizi, Xolmamatova Shoxista Sobir qizi, Zayidova Shaboda Sodiqovna</t>
+          <t>Ma'lumotlar hali hujjat bilan tasdiqlanmagan</t>
         </is>
       </c>
       <c r="I32" s="17" t="inlineStr">
         <is>
-          <t>Aka-uka/opa-singil bo'lishi mumkin — tekshiring</t>
+          <t>Hujjat nusxasi bilan solishtirib tasdiqlang</t>
         </is>
       </c>
       <c r="J32" s="17" t="inlineStr">
@@ -2414,44 +2410,40 @@
       </c>
       <c r="C33" s="17" t="inlineStr">
         <is>
-          <t>26-03</t>
+          <t>26-04</t>
         </is>
       </c>
       <c r="D33" s="17" t="inlineStr">
         <is>
-          <t>Xolmaxmatova Sevinch Isomiddin qizi</t>
+          <t>Xurramova Shahnoza Shuhrat qizi</t>
         </is>
       </c>
       <c r="E33" s="17" t="inlineStr">
         <is>
-          <t>108</t>
+          <t>29</t>
         </is>
       </c>
       <c r="F33" s="17" t="inlineStr">
         <is>
-          <t>Yashash viloyat+tumani</t>
+          <t>Telefon</t>
         </is>
       </c>
       <c r="G33" s="17" t="inlineStr">
         <is>
-          <t>PINFL hudud kodi 573</t>
+          <t>880096166</t>
         </is>
       </c>
       <c r="H33" s="17" t="inlineStr">
         <is>
-          <t>Yashash hududi aniqlanmadi (muassasa nomida tuman yo'q, PINFL hudud kodi noma'lum)</t>
+          <t>Bir xil telefon raqami: Xurramova Shahnoza Shuhrat qizi, Xurramova Shahrizoda Shuhrat qizi</t>
         </is>
       </c>
       <c r="I33" s="17" t="inlineStr">
         <is>
-          <t>Shablonda bo'sh qoldirildi — qo'lda kiriting</t>
-        </is>
-      </c>
-      <c r="J33" s="17" t="inlineStr">
-        <is>
-          <t>Ha</t>
-        </is>
-      </c>
+          <t>Aka-uka/opa-singil bo'lishi mumkin — tekshiring</t>
+        </is>
+      </c>
+      <c r="J33" s="17" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="17" t="n">
@@ -2464,37 +2456,37 @@
       </c>
       <c r="C34" s="17" t="inlineStr">
         <is>
-          <t>26-03</t>
+          <t>26-04</t>
         </is>
       </c>
       <c r="D34" s="17" t="inlineStr">
         <is>
-          <t>Xurramova Sabina Yuldosh qizi</t>
+          <t>Xurramova Shahrizoda Shuhrat qizi</t>
         </is>
       </c>
       <c r="E34" s="17" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>96</t>
         </is>
       </c>
       <c r="F34" s="17" t="inlineStr">
         <is>
-          <t>Yashash viloyat+tumani</t>
+          <t>Telefon</t>
         </is>
       </c>
       <c r="G34" s="17" t="inlineStr">
         <is>
-          <t>PINFL hudud kodi 823</t>
+          <t>880096166</t>
         </is>
       </c>
       <c r="H34" s="17" t="inlineStr">
         <is>
-          <t>Yashash hududi aniqlanmadi (muassasa nomida tuman yo'q, PINFL hudud kodi noma'lum)</t>
+          <t>Bir xil telefon raqami: Xurramova Shahnoza Shuhrat qizi, Xurramova Shahrizoda Shuhrat qizi</t>
         </is>
       </c>
       <c r="I34" s="17" t="inlineStr">
         <is>
-          <t>Shablonda bo'sh qoldirildi — qo'lda kiriting</t>
+          <t>Aka-uka/opa-singil bo'lishi mumkin — tekshiring</t>
         </is>
       </c>
       <c r="J34" s="17" t="inlineStr">
@@ -2514,37 +2506,37 @@
       </c>
       <c r="C35" s="17" t="inlineStr">
         <is>
-          <t>26-03</t>
+          <t>26-04</t>
         </is>
       </c>
       <c r="D35" s="17" t="inlineStr">
         <is>
-          <t>Xurramova Sabina Yuldosh qizi</t>
+          <t>Zayidova Shaboda Sodiqovna</t>
         </is>
       </c>
       <c r="E35" s="17" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>387</t>
         </is>
       </c>
       <c r="F35" s="17" t="inlineStr">
         <is>
-          <t>Tasdiq</t>
+          <t>Telefon</t>
         </is>
       </c>
       <c r="G35" s="17" t="inlineStr">
         <is>
-          <t>KUTILMOQDA</t>
+          <t>908785105</t>
         </is>
       </c>
       <c r="H35" s="17" t="inlineStr">
         <is>
-          <t>Ma'lumotlar hali hujjat bilan tasdiqlanmagan</t>
+          <t>Bir xil telefon raqami: Quysinova Rohshona To'lqin qizi, Xolmamatova Shoxista Sobir qizi, Zayidova Shaboda Sodiqovna</t>
         </is>
       </c>
       <c r="I35" s="17" t="inlineStr">
         <is>
-          <t>Hujjat nusxasi bilan solishtirib tasdiqlang</t>
+          <t>Aka-uka/opa-singil bo'lishi mumkin — tekshiring</t>
         </is>
       </c>
       <c r="J35" s="17" t="inlineStr">
@@ -2569,35 +2561,39 @@
       </c>
       <c r="D36" s="17" t="inlineStr">
         <is>
-          <t>Jalolov Javlonbek G'ani o'g'li</t>
+          <t>Zayidova Shaboda Sodiqovna</t>
         </is>
       </c>
       <c r="E36" s="17" t="inlineStr">
         <is>
-          <t>211</t>
+          <t>387</t>
         </is>
       </c>
       <c r="F36" s="17" t="inlineStr">
         <is>
-          <t>Pasport</t>
+          <t>Telefon</t>
         </is>
       </c>
       <c r="G36" s="17" t="inlineStr">
         <is>
-          <t>AE 4994200</t>
+          <t>916397685</t>
         </is>
       </c>
       <c r="H36" s="17" t="inlineStr">
         <is>
-          <t>Pasport raqamida bo'shliq / kichik harf bor</t>
+          <t>Bir xil telefon raqami: Quysinova Rohshona To'lqin qizi, Xolmamatova Shoxista Sobir qizi, Zayidova Shaboda Sodiqovna</t>
         </is>
       </c>
       <c r="I36" s="17" t="inlineStr">
         <is>
-          <t>To'g'ri yozilishi: AE4994200 (shablonda tozalandi)</t>
-        </is>
-      </c>
-      <c r="J36" s="17" t="inlineStr"/>
+          <t>Aka-uka/opa-singil bo'lishi mumkin — tekshiring</t>
+        </is>
+      </c>
+      <c r="J36" s="17" t="inlineStr">
+        <is>
+          <t>Ha</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="17" t="n">
@@ -2610,40 +2606,44 @@
       </c>
       <c r="C37" s="17" t="inlineStr">
         <is>
-          <t>26-04</t>
+          <t>26-05</t>
         </is>
       </c>
       <c r="D37" s="17" t="inlineStr">
         <is>
-          <t>Nafasova Sevinch Bollijon qizi</t>
+          <t>Ergasheva Shabbona Shodmon qizi</t>
         </is>
       </c>
       <c r="E37" s="17" t="inlineStr">
         <is>
-          <t>266</t>
+          <t>123</t>
         </is>
       </c>
       <c r="F37" s="17" t="inlineStr">
         <is>
-          <t>Yashash viloyat+tumani</t>
+          <t>Telefon</t>
         </is>
       </c>
       <c r="G37" s="17" t="inlineStr">
         <is>
-          <t>PINFL hudud kodi 573</t>
+          <t>914551195</t>
         </is>
       </c>
       <c r="H37" s="17" t="inlineStr">
         <is>
-          <t>Yashash hududi aniqlanmadi (muassasa nomida tuman yo'q, PINFL hudud kodi noma'lum)</t>
+          <t>Bir xil telefon raqami: Ergasheva Shabbona Shodmon qizi, Yuldosheva Ruhshona Xabibullo qizi</t>
         </is>
       </c>
       <c r="I37" s="17" t="inlineStr">
         <is>
-          <t>Shablonda bo'sh qoldirildi — qo'lda kiriting</t>
-        </is>
-      </c>
-      <c r="J37" s="17" t="inlineStr"/>
+          <t>Aka-uka/opa-singil bo'lishi mumkin — tekshiring</t>
+        </is>
+      </c>
+      <c r="J37" s="17" t="inlineStr">
+        <is>
+          <t>Ha</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="17" t="n">
@@ -2656,44 +2656,36 @@
       </c>
       <c r="C38" s="17" t="inlineStr">
         <is>
-          <t>26-04</t>
+          <t>26-05</t>
         </is>
       </c>
       <c r="D38" s="17" t="inlineStr">
         <is>
-          <t>Ulugbekova Zara Ulug'bek qizi</t>
+          <t>Nazarova Munisa Erkin qizi</t>
         </is>
       </c>
       <c r="E38" s="17" t="inlineStr">
         <is>
-          <t>313</t>
+          <t>258</t>
         </is>
       </c>
       <c r="F38" s="17" t="inlineStr">
         <is>
-          <t>Tasdiq</t>
+          <t>Holat</t>
         </is>
       </c>
       <c r="G38" s="17" t="inlineStr">
         <is>
-          <t>KUTILMOQDA</t>
+          <t>chala</t>
         </is>
       </c>
       <c r="H38" s="17" t="inlineStr">
         <is>
-          <t>Ma'lumotlar hali hujjat bilan tasdiqlanmagan</t>
-        </is>
-      </c>
-      <c r="I38" s="17" t="inlineStr">
-        <is>
-          <t>Hujjat nusxasi bilan solishtirib tasdiqlang</t>
-        </is>
-      </c>
-      <c r="J38" s="17" t="inlineStr">
-        <is>
-          <t>Ha</t>
-        </is>
-      </c>
+          <t>Hujjatlar to'liq emas (status: chala)</t>
+        </is>
+      </c>
+      <c r="I38" s="17" t="inlineStr"/>
+      <c r="J38" s="17" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="17" t="n">
@@ -2706,19 +2698,15 @@
       </c>
       <c r="C39" s="17" t="inlineStr">
         <is>
-          <t>26-04</t>
+          <t>26-05</t>
         </is>
       </c>
       <c r="D39" s="17" t="inlineStr">
         <is>
-          <t>Xujamuratova Durdona Bahrom qizi</t>
-        </is>
-      </c>
-      <c r="E39" s="17" t="inlineStr">
-        <is>
-          <t>232</t>
-        </is>
-      </c>
+          <t>Ne'matova Sevinch Hikmatullo qizi</t>
+        </is>
+      </c>
+      <c r="E39" s="17" t="inlineStr"/>
       <c r="F39" s="17" t="inlineStr">
         <is>
           <t>Tasdiq</t>
@@ -2756,17 +2744,17 @@
       </c>
       <c r="C40" s="17" t="inlineStr">
         <is>
-          <t>26-04</t>
+          <t>26-05</t>
         </is>
       </c>
       <c r="D40" s="17" t="inlineStr">
         <is>
-          <t>Xurramova Shahnoza Shuhrat qizi</t>
+          <t>Tursunova Fotima Qosim qizi</t>
         </is>
       </c>
       <c r="E40" s="17" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>218</t>
         </is>
       </c>
       <c r="F40" s="17" t="inlineStr">
@@ -2776,12 +2764,12 @@
       </c>
       <c r="G40" s="17" t="inlineStr">
         <is>
-          <t>880096166</t>
+          <t>995658681</t>
         </is>
       </c>
       <c r="H40" s="17" t="inlineStr">
         <is>
-          <t>Bir xil telefon raqami: Xurramova Shahnoza Shuhrat qizi, Xurramova Shahrizoda Shuhrat qizi</t>
+          <t>Bir xil telefon raqami: Tursunov Sohibjon Hakim o'g'li, Tursunova Fotima Qosim qizi, Tursunova Zuhra Qosim qizi</t>
         </is>
       </c>
       <c r="I40" s="17" t="inlineStr">
@@ -2789,7 +2777,11 @@
           <t>Aka-uka/opa-singil bo'lishi mumkin — tekshiring</t>
         </is>
       </c>
-      <c r="J40" s="17" t="inlineStr"/>
+      <c r="J40" s="17" t="inlineStr">
+        <is>
+          <t>Ha</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="17" t="n">
@@ -2802,17 +2794,17 @@
       </c>
       <c r="C41" s="17" t="inlineStr">
         <is>
-          <t>26-04</t>
+          <t>26-05</t>
         </is>
       </c>
       <c r="D41" s="17" t="inlineStr">
         <is>
-          <t>Xurramova Shahrizoda Shuhrat qizi</t>
+          <t>Tursunova Zuhra Qosim qizi</t>
         </is>
       </c>
       <c r="E41" s="17" t="inlineStr">
         <is>
-          <t>96</t>
+          <t>219</t>
         </is>
       </c>
       <c r="F41" s="17" t="inlineStr">
@@ -2822,12 +2814,12 @@
       </c>
       <c r="G41" s="17" t="inlineStr">
         <is>
-          <t>880096166</t>
+          <t>995658681</t>
         </is>
       </c>
       <c r="H41" s="17" t="inlineStr">
         <is>
-          <t>Bir xil telefon raqami: Xurramova Shahnoza Shuhrat qizi, Xurramova Shahrizoda Shuhrat qizi</t>
+          <t>Bir xil telefon raqami: Tursunov Sohibjon Hakim o'g'li, Tursunova Fotima Qosim qizi, Tursunova Zuhra Qosim qizi</t>
         </is>
       </c>
       <c r="I41" s="17" t="inlineStr">
@@ -2852,17 +2844,17 @@
       </c>
       <c r="C42" s="17" t="inlineStr">
         <is>
-          <t>26-04</t>
+          <t>26-05</t>
         </is>
       </c>
       <c r="D42" s="17" t="inlineStr">
         <is>
-          <t>Zayidova Shaboda Sodiqovna</t>
+          <t>Yuldosheva Ruhshona Xabibullo qizi</t>
         </is>
       </c>
       <c r="E42" s="17" t="inlineStr">
         <is>
-          <t>387</t>
+          <t>118</t>
         </is>
       </c>
       <c r="F42" s="17" t="inlineStr">
@@ -2872,12 +2864,12 @@
       </c>
       <c r="G42" s="17" t="inlineStr">
         <is>
-          <t>916397685</t>
+          <t>914551195</t>
         </is>
       </c>
       <c r="H42" s="17" t="inlineStr">
         <is>
-          <t>Bir xil telefon raqami: Quysinova Rohshona To'lqin qizi, Xolmamatova Shoxista Sobir qizi, Zayidova Shaboda Sodiqovna</t>
+          <t>Bir xil telefon raqami: Ergasheva Shabbona Shodmon qizi, Yuldosheva Ruhshona Xabibullo qizi</t>
         </is>
       </c>
       <c r="I42" s="17" t="inlineStr">
@@ -2902,37 +2894,37 @@
       </c>
       <c r="C43" s="17" t="inlineStr">
         <is>
-          <t>26-04</t>
+          <t>26-06</t>
         </is>
       </c>
       <c r="D43" s="17" t="inlineStr">
         <is>
-          <t>Zayidova Shaboda Sodiqovna</t>
+          <t>Niyozova Sevara Turoqulovna</t>
         </is>
       </c>
       <c r="E43" s="17" t="inlineStr">
         <is>
-          <t>387</t>
+          <t>304</t>
         </is>
       </c>
       <c r="F43" s="17" t="inlineStr">
         <is>
-          <t>Telefon</t>
+          <t>JSHSHIR</t>
         </is>
       </c>
       <c r="G43" s="17" t="inlineStr">
         <is>
-          <t>908785105</t>
+          <t>412068 9256 0120</t>
         </is>
       </c>
       <c r="H43" s="17" t="inlineStr">
         <is>
-          <t>Bir xil telefon raqami: Quysinova Rohshona To'lqin qizi, Xolmamatova Shoxista Sobir qizi, Zayidova Shaboda Sodiqovna</t>
+          <t>JSHSHIR ichida bo'shliq / ortiqcha belgi bor</t>
         </is>
       </c>
       <c r="I43" s="17" t="inlineStr">
         <is>
-          <t>Aka-uka/opa-singil bo'lishi mumkin — tekshiring</t>
+          <t>To'g'ri yozilishi: 41206892560120 (shablonda tozalandi)</t>
         </is>
       </c>
       <c r="J43" s="17" t="inlineStr">
@@ -2952,37 +2944,37 @@
       </c>
       <c r="C44" s="17" t="inlineStr">
         <is>
-          <t>26-05</t>
+          <t>26-06</t>
         </is>
       </c>
       <c r="D44" s="17" t="inlineStr">
         <is>
-          <t>Ergasheva Shabbona Shodmon qizi</t>
+          <t>Niyozova Sevara Turoqulovna</t>
         </is>
       </c>
       <c r="E44" s="17" t="inlineStr">
         <is>
-          <t>123</t>
+          <t>304</t>
         </is>
       </c>
       <c r="F44" s="17" t="inlineStr">
         <is>
-          <t>Telefon</t>
+          <t>Tasdiq</t>
         </is>
       </c>
       <c r="G44" s="17" t="inlineStr">
         <is>
-          <t>914551195</t>
+          <t>KUTILMOQDA</t>
         </is>
       </c>
       <c r="H44" s="17" t="inlineStr">
         <is>
-          <t>Bir xil telefon raqami: Ergasheva Shabbona Shodmon qizi, Yuldosheva Ruhshona Xabibullo qizi</t>
+          <t>Ma'lumotlar hali hujjat bilan tasdiqlanmagan</t>
         </is>
       </c>
       <c r="I44" s="17" t="inlineStr">
         <is>
-          <t>Aka-uka/opa-singil bo'lishi mumkin — tekshiring</t>
+          <t>Hujjat nusxasi bilan solishtirib tasdiqlang</t>
         </is>
       </c>
       <c r="J44" s="17" t="inlineStr">
@@ -3002,44 +2994,36 @@
       </c>
       <c r="C45" s="17" t="inlineStr">
         <is>
-          <t>26-05</t>
+          <t>26-06</t>
         </is>
       </c>
       <c r="D45" s="17" t="inlineStr">
         <is>
-          <t>Jurayeva Madina Odil qizi</t>
-        </is>
-      </c>
-      <c r="E45" s="17" t="inlineStr">
-        <is>
-          <t>215</t>
-        </is>
-      </c>
+          <t>Sayfieva Sarvinoz Zafar qizi</t>
+        </is>
+      </c>
+      <c r="E45" s="17" t="inlineStr"/>
       <c r="F45" s="17" t="inlineStr">
         <is>
-          <t>Yashash viloyat+tumani</t>
+          <t>JSHSHIR</t>
         </is>
       </c>
       <c r="G45" s="17" t="inlineStr">
         <is>
-          <t>PINFL hudud kodi 573</t>
+          <t>415079 8559 0074</t>
         </is>
       </c>
       <c r="H45" s="17" t="inlineStr">
         <is>
-          <t>Yashash hududi aniqlanmadi (muassasa nomida tuman yo'q, PINFL hudud kodi noma'lum)</t>
+          <t>JSHSHIR ichida bo'shliq / ortiqcha belgi bor</t>
         </is>
       </c>
       <c r="I45" s="17" t="inlineStr">
         <is>
-          <t>Shablonda bo'sh qoldirildi — qo'lda kiriting</t>
-        </is>
-      </c>
-      <c r="J45" s="17" t="inlineStr">
-        <is>
-          <t>Ha</t>
-        </is>
-      </c>
+          <t>To'g'ri yozilishi: 41507985590074 (shablonda tozalandi)</t>
+        </is>
+      </c>
+      <c r="J45" s="17" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" s="17" t="n">
@@ -3052,35 +3036,35 @@
       </c>
       <c r="C46" s="17" t="inlineStr">
         <is>
-          <t>26-05</t>
+          <t>26-06</t>
         </is>
       </c>
       <c r="D46" s="17" t="inlineStr">
         <is>
-          <t>Nazarova Munisa Erkin qizi</t>
-        </is>
-      </c>
-      <c r="E46" s="17" t="inlineStr">
-        <is>
-          <t>258</t>
-        </is>
-      </c>
+          <t>Sayfieva Sarvinoz Zafar qizi</t>
+        </is>
+      </c>
+      <c r="E46" s="17" t="inlineStr"/>
       <c r="F46" s="17" t="inlineStr">
         <is>
-          <t>Holat</t>
+          <t>Tasdiq</t>
         </is>
       </c>
       <c r="G46" s="17" t="inlineStr">
         <is>
-          <t>chala</t>
+          <t>KUTILMOQDA</t>
         </is>
       </c>
       <c r="H46" s="17" t="inlineStr">
         <is>
-          <t>Hujjatlar to'liq emas (status: chala)</t>
-        </is>
-      </c>
-      <c r="I46" s="17" t="inlineStr"/>
+          <t>Ma'lumotlar hali hujjat bilan tasdiqlanmagan</t>
+        </is>
+      </c>
+      <c r="I46" s="17" t="inlineStr">
+        <is>
+          <t>Hujjat nusxasi bilan solishtirib tasdiqlang</t>
+        </is>
+      </c>
       <c r="J46" s="17" t="inlineStr"/>
     </row>
     <row r="47">
@@ -3094,33 +3078,33 @@
       </c>
       <c r="C47" s="17" t="inlineStr">
         <is>
-          <t>26-05</t>
+          <t>26-06</t>
         </is>
       </c>
       <c r="D47" s="17" t="inlineStr">
         <is>
-          <t>Ne'matova Sevinch Hikmatullo qizi</t>
+          <t>Uzoqova Fazilat Nurali qizi</t>
         </is>
       </c>
       <c r="E47" s="17" t="inlineStr"/>
       <c r="F47" s="17" t="inlineStr">
         <is>
-          <t>Tasdiq</t>
+          <t>JSHSHIR</t>
         </is>
       </c>
       <c r="G47" s="17" t="inlineStr">
         <is>
-          <t>KUTILMOQDA</t>
+          <t>407129 0256 0079</t>
         </is>
       </c>
       <c r="H47" s="17" t="inlineStr">
         <is>
-          <t>Ma'lumotlar hali hujjat bilan tasdiqlanmagan</t>
+          <t>JSHSHIR ichida bo'shliq / ortiqcha belgi bor</t>
         </is>
       </c>
       <c r="I47" s="17" t="inlineStr">
         <is>
-          <t>Hujjat nusxasi bilan solishtirib tasdiqlang</t>
+          <t>To'g'ri yozilishi: 40712902560079 (shablonda tozalandi)</t>
         </is>
       </c>
       <c r="J47" s="17" t="inlineStr">
@@ -3140,37 +3124,33 @@
       </c>
       <c r="C48" s="17" t="inlineStr">
         <is>
-          <t>26-05</t>
+          <t>26-06</t>
         </is>
       </c>
       <c r="D48" s="17" t="inlineStr">
         <is>
-          <t>Tursunova Fotima Qosim qizi</t>
-        </is>
-      </c>
-      <c r="E48" s="17" t="inlineStr">
-        <is>
-          <t>218</t>
-        </is>
-      </c>
+          <t>Uzoqova Fazilat Nurali qizi</t>
+        </is>
+      </c>
+      <c r="E48" s="17" t="inlineStr"/>
       <c r="F48" s="17" t="inlineStr">
         <is>
-          <t>Telefon</t>
+          <t>Pasport</t>
         </is>
       </c>
       <c r="G48" s="17" t="inlineStr">
         <is>
-          <t>995658681</t>
+          <t>AE 4385291</t>
         </is>
       </c>
       <c r="H48" s="17" t="inlineStr">
         <is>
-          <t>Bir xil telefon raqami: Tursunov Sohibjon Hakim o'g'li, Tursunova Fotima Qosim qizi, Tursunova Zuhra Qosim qizi</t>
+          <t>Pasport raqamida bo'shliq / kichik harf bor</t>
         </is>
       </c>
       <c r="I48" s="17" t="inlineStr">
         <is>
-          <t>Aka-uka/opa-singil bo'lishi mumkin — tekshiring</t>
+          <t>To'g'ri yozilishi: AE4385291 (shablonda tozalandi)</t>
         </is>
       </c>
       <c r="J48" s="17" t="inlineStr">
@@ -3190,37 +3170,33 @@
       </c>
       <c r="C49" s="17" t="inlineStr">
         <is>
-          <t>26-05</t>
+          <t>26-06</t>
         </is>
       </c>
       <c r="D49" s="17" t="inlineStr">
         <is>
-          <t>Tursunova Zuhra Qosim qizi</t>
-        </is>
-      </c>
-      <c r="E49" s="17" t="inlineStr">
-        <is>
-          <t>219</t>
-        </is>
-      </c>
+          <t>Uzoqova Fazilat Nurali qizi</t>
+        </is>
+      </c>
+      <c r="E49" s="17" t="inlineStr"/>
       <c r="F49" s="17" t="inlineStr">
         <is>
-          <t>Telefon</t>
+          <t>Tasdiq</t>
         </is>
       </c>
       <c r="G49" s="17" t="inlineStr">
         <is>
-          <t>995658681</t>
+          <t>KUTILMOQDA</t>
         </is>
       </c>
       <c r="H49" s="17" t="inlineStr">
         <is>
-          <t>Bir xil telefon raqami: Tursunov Sohibjon Hakim o'g'li, Tursunova Fotima Qosim qizi, Tursunova Zuhra Qosim qizi</t>
+          <t>Ma'lumotlar hali hujjat bilan tasdiqlanmagan</t>
         </is>
       </c>
       <c r="I49" s="17" t="inlineStr">
         <is>
-          <t>Aka-uka/opa-singil bo'lishi mumkin — tekshiring</t>
+          <t>Hujjat nusxasi bilan solishtirib tasdiqlang</t>
         </is>
       </c>
       <c r="J49" s="17" t="inlineStr">
@@ -3229,476 +3205,8 @@
         </is>
       </c>
     </row>
-    <row r="50">
-      <c r="A50" s="17" t="n">
-        <v>49</v>
-      </c>
-      <c r="B50" s="19" t="inlineStr">
-        <is>
-          <t>Past</t>
-        </is>
-      </c>
-      <c r="C50" s="17" t="inlineStr">
-        <is>
-          <t>26-05</t>
-        </is>
-      </c>
-      <c r="D50" s="17" t="inlineStr">
-        <is>
-          <t>Yuldosheva Ruhshona Xabibullo qizi</t>
-        </is>
-      </c>
-      <c r="E50" s="17" t="inlineStr">
-        <is>
-          <t>118</t>
-        </is>
-      </c>
-      <c r="F50" s="17" t="inlineStr">
-        <is>
-          <t>Telefon</t>
-        </is>
-      </c>
-      <c r="G50" s="17" t="inlineStr">
-        <is>
-          <t>914551195</t>
-        </is>
-      </c>
-      <c r="H50" s="17" t="inlineStr">
-        <is>
-          <t>Bir xil telefon raqami: Ergasheva Shabbona Shodmon qizi, Yuldosheva Ruhshona Xabibullo qizi</t>
-        </is>
-      </c>
-      <c r="I50" s="17" t="inlineStr">
-        <is>
-          <t>Aka-uka/opa-singil bo'lishi mumkin — tekshiring</t>
-        </is>
-      </c>
-      <c r="J50" s="17" t="inlineStr">
-        <is>
-          <t>Ha</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" s="17" t="n">
-        <v>50</v>
-      </c>
-      <c r="B51" s="19" t="inlineStr">
-        <is>
-          <t>Past</t>
-        </is>
-      </c>
-      <c r="C51" s="17" t="inlineStr">
-        <is>
-          <t>26-06</t>
-        </is>
-      </c>
-      <c r="D51" s="17" t="inlineStr">
-        <is>
-          <t>Eshimova Zilola Bekzod qizi</t>
-        </is>
-      </c>
-      <c r="E51" s="17" t="inlineStr">
-        <is>
-          <t>174</t>
-        </is>
-      </c>
-      <c r="F51" s="17" t="inlineStr">
-        <is>
-          <t>Yashash viloyat+tumani</t>
-        </is>
-      </c>
-      <c r="G51" s="17" t="inlineStr">
-        <is>
-          <t>PINFL hudud kodi 573</t>
-        </is>
-      </c>
-      <c r="H51" s="17" t="inlineStr">
-        <is>
-          <t>Yashash hududi aniqlanmadi (muassasa nomida tuman yo'q, PINFL hudud kodi noma'lum)</t>
-        </is>
-      </c>
-      <c r="I51" s="17" t="inlineStr">
-        <is>
-          <t>Shablonda bo'sh qoldirildi — qo'lda kiriting</t>
-        </is>
-      </c>
-      <c r="J51" s="17" t="inlineStr">
-        <is>
-          <t>Ha</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="17" t="n">
-        <v>51</v>
-      </c>
-      <c r="B52" s="19" t="inlineStr">
-        <is>
-          <t>Past</t>
-        </is>
-      </c>
-      <c r="C52" s="17" t="inlineStr">
-        <is>
-          <t>26-06</t>
-        </is>
-      </c>
-      <c r="D52" s="17" t="inlineStr">
-        <is>
-          <t>Niyozova Sevara Turoqulovna</t>
-        </is>
-      </c>
-      <c r="E52" s="17" t="inlineStr">
-        <is>
-          <t>304</t>
-        </is>
-      </c>
-      <c r="F52" s="17" t="inlineStr">
-        <is>
-          <t>JSHSHIR</t>
-        </is>
-      </c>
-      <c r="G52" s="17" t="inlineStr">
-        <is>
-          <t>412068 9256 0120</t>
-        </is>
-      </c>
-      <c r="H52" s="17" t="inlineStr">
-        <is>
-          <t>JSHSHIR ichida bo'shliq / ortiqcha belgi bor</t>
-        </is>
-      </c>
-      <c r="I52" s="17" t="inlineStr">
-        <is>
-          <t>To'g'ri yozilishi: 41206892560120 (shablonda tozalandi)</t>
-        </is>
-      </c>
-      <c r="J52" s="17" t="inlineStr">
-        <is>
-          <t>Ha</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" s="17" t="n">
-        <v>52</v>
-      </c>
-      <c r="B53" s="19" t="inlineStr">
-        <is>
-          <t>Past</t>
-        </is>
-      </c>
-      <c r="C53" s="17" t="inlineStr">
-        <is>
-          <t>26-06</t>
-        </is>
-      </c>
-      <c r="D53" s="17" t="inlineStr">
-        <is>
-          <t>Niyozova Sevara Turoqulovna</t>
-        </is>
-      </c>
-      <c r="E53" s="17" t="inlineStr">
-        <is>
-          <t>304</t>
-        </is>
-      </c>
-      <c r="F53" s="17" t="inlineStr">
-        <is>
-          <t>Tasdiq</t>
-        </is>
-      </c>
-      <c r="G53" s="17" t="inlineStr">
-        <is>
-          <t>KUTILMOQDA</t>
-        </is>
-      </c>
-      <c r="H53" s="17" t="inlineStr">
-        <is>
-          <t>Ma'lumotlar hali hujjat bilan tasdiqlanmagan</t>
-        </is>
-      </c>
-      <c r="I53" s="17" t="inlineStr">
-        <is>
-          <t>Hujjat nusxasi bilan solishtirib tasdiqlang</t>
-        </is>
-      </c>
-      <c r="J53" s="17" t="inlineStr">
-        <is>
-          <t>Ha</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" s="17" t="n">
-        <v>53</v>
-      </c>
-      <c r="B54" s="19" t="inlineStr">
-        <is>
-          <t>Past</t>
-        </is>
-      </c>
-      <c r="C54" s="17" t="inlineStr">
-        <is>
-          <t>26-06</t>
-        </is>
-      </c>
-      <c r="D54" s="17" t="inlineStr">
-        <is>
-          <t>Sayfieva Sarvinoz Zafar qizi</t>
-        </is>
-      </c>
-      <c r="E54" s="17" t="inlineStr"/>
-      <c r="F54" s="17" t="inlineStr">
-        <is>
-          <t>JSHSHIR</t>
-        </is>
-      </c>
-      <c r="G54" s="17" t="inlineStr">
-        <is>
-          <t>415079 8559 0074</t>
-        </is>
-      </c>
-      <c r="H54" s="17" t="inlineStr">
-        <is>
-          <t>JSHSHIR ichida bo'shliq / ortiqcha belgi bor</t>
-        </is>
-      </c>
-      <c r="I54" s="17" t="inlineStr">
-        <is>
-          <t>To'g'ri yozilishi: 41507985590074 (shablonda tozalandi)</t>
-        </is>
-      </c>
-      <c r="J54" s="17" t="inlineStr"/>
-    </row>
-    <row r="55">
-      <c r="A55" s="17" t="n">
-        <v>54</v>
-      </c>
-      <c r="B55" s="19" t="inlineStr">
-        <is>
-          <t>Past</t>
-        </is>
-      </c>
-      <c r="C55" s="17" t="inlineStr">
-        <is>
-          <t>26-06</t>
-        </is>
-      </c>
-      <c r="D55" s="17" t="inlineStr">
-        <is>
-          <t>Sayfieva Sarvinoz Zafar qizi</t>
-        </is>
-      </c>
-      <c r="E55" s="17" t="inlineStr"/>
-      <c r="F55" s="17" t="inlineStr">
-        <is>
-          <t>Tasdiq</t>
-        </is>
-      </c>
-      <c r="G55" s="17" t="inlineStr">
-        <is>
-          <t>KUTILMOQDA</t>
-        </is>
-      </c>
-      <c r="H55" s="17" t="inlineStr">
-        <is>
-          <t>Ma'lumotlar hali hujjat bilan tasdiqlanmagan</t>
-        </is>
-      </c>
-      <c r="I55" s="17" t="inlineStr">
-        <is>
-          <t>Hujjat nusxasi bilan solishtirib tasdiqlang</t>
-        </is>
-      </c>
-      <c r="J55" s="17" t="inlineStr"/>
-    </row>
-    <row r="56">
-      <c r="A56" s="17" t="n">
-        <v>55</v>
-      </c>
-      <c r="B56" s="19" t="inlineStr">
-        <is>
-          <t>Past</t>
-        </is>
-      </c>
-      <c r="C56" s="17" t="inlineStr">
-        <is>
-          <t>26-06</t>
-        </is>
-      </c>
-      <c r="D56" s="17" t="inlineStr">
-        <is>
-          <t>Sayfillayeva Shodiyona Sayfilla qizi</t>
-        </is>
-      </c>
-      <c r="E56" s="17" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="F56" s="17" t="inlineStr">
-        <is>
-          <t>Yashash viloyat+tumani</t>
-        </is>
-      </c>
-      <c r="G56" s="17" t="inlineStr">
-        <is>
-          <t>PINFL hudud kodi 573</t>
-        </is>
-      </c>
-      <c r="H56" s="17" t="inlineStr">
-        <is>
-          <t>Yashash hududi aniqlanmadi (muassasa nomida tuman yo'q, PINFL hudud kodi noma'lum)</t>
-        </is>
-      </c>
-      <c r="I56" s="17" t="inlineStr">
-        <is>
-          <t>Shablonda bo'sh qoldirildi — qo'lda kiriting</t>
-        </is>
-      </c>
-      <c r="J56" s="17" t="inlineStr"/>
-    </row>
-    <row r="57">
-      <c r="A57" s="17" t="n">
-        <v>56</v>
-      </c>
-      <c r="B57" s="19" t="inlineStr">
-        <is>
-          <t>Past</t>
-        </is>
-      </c>
-      <c r="C57" s="17" t="inlineStr">
-        <is>
-          <t>26-06</t>
-        </is>
-      </c>
-      <c r="D57" s="17" t="inlineStr">
-        <is>
-          <t>Uzoqova Fazilat Nurali qizi</t>
-        </is>
-      </c>
-      <c r="E57" s="17" t="inlineStr"/>
-      <c r="F57" s="17" t="inlineStr">
-        <is>
-          <t>JSHSHIR</t>
-        </is>
-      </c>
-      <c r="G57" s="17" t="inlineStr">
-        <is>
-          <t>407129 0256 0079</t>
-        </is>
-      </c>
-      <c r="H57" s="17" t="inlineStr">
-        <is>
-          <t>JSHSHIR ichida bo'shliq / ortiqcha belgi bor</t>
-        </is>
-      </c>
-      <c r="I57" s="17" t="inlineStr">
-        <is>
-          <t>To'g'ri yozilishi: 40712902560079 (shablonda tozalandi)</t>
-        </is>
-      </c>
-      <c r="J57" s="17" t="inlineStr">
-        <is>
-          <t>Ha</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" s="17" t="n">
-        <v>57</v>
-      </c>
-      <c r="B58" s="19" t="inlineStr">
-        <is>
-          <t>Past</t>
-        </is>
-      </c>
-      <c r="C58" s="17" t="inlineStr">
-        <is>
-          <t>26-06</t>
-        </is>
-      </c>
-      <c r="D58" s="17" t="inlineStr">
-        <is>
-          <t>Uzoqova Fazilat Nurali qizi</t>
-        </is>
-      </c>
-      <c r="E58" s="17" t="inlineStr"/>
-      <c r="F58" s="17" t="inlineStr">
-        <is>
-          <t>Pasport</t>
-        </is>
-      </c>
-      <c r="G58" s="17" t="inlineStr">
-        <is>
-          <t>AE 4385291</t>
-        </is>
-      </c>
-      <c r="H58" s="17" t="inlineStr">
-        <is>
-          <t>Pasport raqamida bo'shliq / kichik harf bor</t>
-        </is>
-      </c>
-      <c r="I58" s="17" t="inlineStr">
-        <is>
-          <t>To'g'ri yozilishi: AE4385291 (shablonda tozalandi)</t>
-        </is>
-      </c>
-      <c r="J58" s="17" t="inlineStr">
-        <is>
-          <t>Ha</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" s="17" t="n">
-        <v>58</v>
-      </c>
-      <c r="B59" s="19" t="inlineStr">
-        <is>
-          <t>Past</t>
-        </is>
-      </c>
-      <c r="C59" s="17" t="inlineStr">
-        <is>
-          <t>26-06</t>
-        </is>
-      </c>
-      <c r="D59" s="17" t="inlineStr">
-        <is>
-          <t>Uzoqova Fazilat Nurali qizi</t>
-        </is>
-      </c>
-      <c r="E59" s="17" t="inlineStr"/>
-      <c r="F59" s="17" t="inlineStr">
-        <is>
-          <t>Tasdiq</t>
-        </is>
-      </c>
-      <c r="G59" s="17" t="inlineStr">
-        <is>
-          <t>KUTILMOQDA</t>
-        </is>
-      </c>
-      <c r="H59" s="17" t="inlineStr">
-        <is>
-          <t>Ma'lumotlar hali hujjat bilan tasdiqlanmagan</t>
-        </is>
-      </c>
-      <c r="I59" s="17" t="inlineStr">
-        <is>
-          <t>Hujjat nusxasi bilan solishtirib tasdiqlang</t>
-        </is>
-      </c>
-      <c r="J59" s="17" t="inlineStr">
-        <is>
-          <t>Ha</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:J59"/>
+  <autoFilter ref="A1:J49"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -3709,7 +3217,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G41"/>
+  <dimension ref="A1:G33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -3807,12 +3315,11 @@
         </is>
       </c>
       <c r="E3" s="17" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F3" s="17" t="inlineStr">
         <is>
           <t>• [O'rta] Ism g'ayrioddiy yozilgan (ehtimol 'Murodulla')
-• [Past] Yashash hududi aniqlanmadi (muassasa nomida tuman yo'q, PINFL hudud kodi noma'lum)
 • [Past] Ma'lumotlar hali hujjat bilan tasdiqlanmagan</t>
         </is>
       </c>
@@ -4297,15 +3804,16 @@
       </c>
       <c r="D18" s="17" t="inlineStr">
         <is>
-          <t>Eshnazarova Dilnoza Rustam qizi</t>
+          <t>Izzatulloyeva Vazira G'ayratzoda</t>
         </is>
       </c>
       <c r="E18" s="17" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F18" s="17" t="inlineStr">
         <is>
-          <t>• [Past] Yashash hududi aniqlanmadi (muassasa nomida tuman yo'q, PINFL hudud kodi noma'lum)</t>
+          <t>• [Past] Otasining ismi 'qizi / o'g'li' bilan tugamagan
+• [Past] Ma'lumotlar hali hujjat bilan tasdiqlanmagan</t>
         </is>
       </c>
       <c r="G18" s="17" t="inlineStr">
@@ -4330,7 +3838,7 @@
       </c>
       <c r="D19" s="17" t="inlineStr">
         <is>
-          <t>Fayzullayeva Sarvinoz Sherbobo qizi</t>
+          <t>Niyozova Komila Toshpulatovna</t>
         </is>
       </c>
       <c r="E19" s="17" t="n">
@@ -4338,14 +3846,10 @@
       </c>
       <c r="F19" s="17" t="inlineStr">
         <is>
-          <t>• [Past] Yashash hududi aniqlanmadi (muassasa nomida tuman yo'q, PINFL hudud kodi noma'lum)</t>
-        </is>
-      </c>
-      <c r="G19" s="17" t="inlineStr">
-        <is>
-          <t>Ha</t>
-        </is>
-      </c>
+          <t>• [Past] Ma'lumotlar hali hujjat bilan tasdiqlanmagan</t>
+        </is>
+      </c>
+      <c r="G19" s="17" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="17" t="n">
@@ -4363,16 +3867,15 @@
       </c>
       <c r="D20" s="17" t="inlineStr">
         <is>
-          <t>Izzatulloyeva Vazira G'ayratzoda</t>
+          <t>Primova Husnora Shovkat qizi</t>
         </is>
       </c>
       <c r="E20" s="17" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F20" s="17" t="inlineStr">
         <is>
-          <t>• [Past] Otasining ismi 'qizi / o'g'li' bilan tugamagan
-• [Past] Ma'lumotlar hali hujjat bilan tasdiqlanmagan</t>
+          <t>• [Past] Pasport raqamida bo'shliq / kichik harf bor</t>
         </is>
       </c>
       <c r="G20" s="17" t="inlineStr">
@@ -4397,18 +3900,23 @@
       </c>
       <c r="D21" s="17" t="inlineStr">
         <is>
-          <t>Niyozova Komila Toshpulatovna</t>
+          <t>Xolmamatova Shoxista Sobir qizi</t>
         </is>
       </c>
       <c r="E21" s="17" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F21" s="17" t="inlineStr">
         <is>
-          <t>• [Past] Ma'lumotlar hali hujjat bilan tasdiqlanmagan</t>
-        </is>
-      </c>
-      <c r="G21" s="17" t="inlineStr"/>
+          <t>• [Past] Bir xil telefon raqami: Quysinova Rohshona To'lqin qizi, Xolmamatova Shoxista Sobir qizi, Zayidova Shaboda Sodiqovna
+• [Past] Bir xil telefon raqami: Quysinova Rohshona To'lqin qizi, Xolmamatova Shoxista Sobir qizi, Zayidova Shaboda Sodiqovna</t>
+        </is>
+      </c>
+      <c r="G21" s="17" t="inlineStr">
+        <is>
+          <t>Ha</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="17" t="n">
@@ -4426,7 +3934,7 @@
       </c>
       <c r="D22" s="17" t="inlineStr">
         <is>
-          <t>Primova Husnora Shovkat qizi</t>
+          <t>Xurramova Sabina Yuldosh qizi</t>
         </is>
       </c>
       <c r="E22" s="17" t="n">
@@ -4434,7 +3942,7 @@
       </c>
       <c r="F22" s="17" t="inlineStr">
         <is>
-          <t>• [Past] Pasport raqamida bo'shliq / kichik harf bor</t>
+          <t>• [Past] Ma'lumotlar hali hujjat bilan tasdiqlanmagan</t>
         </is>
       </c>
       <c r="G22" s="17" t="inlineStr">
@@ -4454,12 +3962,12 @@
       </c>
       <c r="C23" s="17" t="inlineStr">
         <is>
-          <t>26-03</t>
+          <t>26-04</t>
         </is>
       </c>
       <c r="D23" s="17" t="inlineStr">
         <is>
-          <t>Shamsiyeva Fotima Sharofiddin qizi</t>
+          <t>Jalolov Javlonbek G'ani o'g'li</t>
         </is>
       </c>
       <c r="E23" s="17" t="n">
@@ -4467,14 +3975,10 @@
       </c>
       <c r="F23" s="17" t="inlineStr">
         <is>
-          <t>• [Past] Yashash hududi aniqlanmadi (muassasa nomida tuman yo'q, PINFL hudud kodi noma'lum)</t>
-        </is>
-      </c>
-      <c r="G23" s="17" t="inlineStr">
-        <is>
-          <t>Ha</t>
-        </is>
-      </c>
+          <t>• [Past] Pasport raqamida bo'shliq / kichik harf bor</t>
+        </is>
+      </c>
+      <c r="G23" s="17" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="17" t="n">
@@ -4487,21 +3991,20 @@
       </c>
       <c r="C24" s="17" t="inlineStr">
         <is>
-          <t>26-03</t>
+          <t>26-04</t>
         </is>
       </c>
       <c r="D24" s="17" t="inlineStr">
         <is>
-          <t>Xolmamatova Shoxista Sobir qizi</t>
+          <t>Ulugbekova Zara Ulug'bek qizi</t>
         </is>
       </c>
       <c r="E24" s="17" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F24" s="17" t="inlineStr">
         <is>
-          <t>• [Past] Bir xil telefon raqami: Quysinova Rohshona To'lqin qizi, Xolmamatova Shoxista Sobir qizi, Zayidova Shaboda Sodiqovna
-• [Past] Bir xil telefon raqami: Quysinova Rohshona To'lqin qizi, Xolmamatova Shoxista Sobir qizi, Zayidova Shaboda Sodiqovna</t>
+          <t>• [Past] Ma'lumotlar hali hujjat bilan tasdiqlanmagan</t>
         </is>
       </c>
       <c r="G24" s="17" t="inlineStr">
@@ -4521,12 +4024,12 @@
       </c>
       <c r="C25" s="17" t="inlineStr">
         <is>
-          <t>26-03</t>
+          <t>26-04</t>
         </is>
       </c>
       <c r="D25" s="17" t="inlineStr">
         <is>
-          <t>Xolmaxmatova Sevinch Isomiddin qizi</t>
+          <t>Xujamuratova Durdona Bahrom qizi</t>
         </is>
       </c>
       <c r="E25" s="17" t="n">
@@ -4534,7 +4037,7 @@
       </c>
       <c r="F25" s="17" t="inlineStr">
         <is>
-          <t>• [Past] Yashash hududi aniqlanmadi (muassasa nomida tuman yo'q, PINFL hudud kodi noma'lum)</t>
+          <t>• [Past] Ma'lumotlar hali hujjat bilan tasdiqlanmagan</t>
         </is>
       </c>
       <c r="G25" s="17" t="inlineStr">
@@ -4554,28 +4057,23 @@
       </c>
       <c r="C26" s="17" t="inlineStr">
         <is>
-          <t>26-03</t>
+          <t>26-04</t>
         </is>
       </c>
       <c r="D26" s="17" t="inlineStr">
         <is>
-          <t>Xurramova Sabina Yuldosh qizi</t>
+          <t>Xurramova Shahnoza Shuhrat qizi</t>
         </is>
       </c>
       <c r="E26" s="17" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F26" s="17" t="inlineStr">
         <is>
-          <t>• [Past] Yashash hududi aniqlanmadi (muassasa nomida tuman yo'q, PINFL hudud kodi noma'lum)
-• [Past] Ma'lumotlar hali hujjat bilan tasdiqlanmagan</t>
-        </is>
-      </c>
-      <c r="G26" s="17" t="inlineStr">
-        <is>
-          <t>Ha</t>
-        </is>
-      </c>
+          <t>• [Past] Bir xil telefon raqami: Xurramova Shahnoza Shuhrat qizi, Xurramova Shahrizoda Shuhrat qizi</t>
+        </is>
+      </c>
+      <c r="G26" s="17" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="17" t="n">
@@ -4593,7 +4091,7 @@
       </c>
       <c r="D27" s="17" t="inlineStr">
         <is>
-          <t>Jalolov Javlonbek G'ani o'g'li</t>
+          <t>Xurramova Shahrizoda Shuhrat qizi</t>
         </is>
       </c>
       <c r="E27" s="17" t="n">
@@ -4601,10 +4099,14 @@
       </c>
       <c r="F27" s="17" t="inlineStr">
         <is>
-          <t>• [Past] Pasport raqamida bo'shliq / kichik harf bor</t>
-        </is>
-      </c>
-      <c r="G27" s="17" t="inlineStr"/>
+          <t>• [Past] Bir xil telefon raqami: Xurramova Shahnoza Shuhrat qizi, Xurramova Shahrizoda Shuhrat qizi</t>
+        </is>
+      </c>
+      <c r="G27" s="17" t="inlineStr">
+        <is>
+          <t>Ha</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="17" t="n">
@@ -4622,18 +4124,23 @@
       </c>
       <c r="D28" s="17" t="inlineStr">
         <is>
-          <t>Nafasova Sevinch Bollijon qizi</t>
+          <t>Zayidova Shaboda Sodiqovna</t>
         </is>
       </c>
       <c r="E28" s="17" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F28" s="17" t="inlineStr">
         <is>
-          <t>• [Past] Yashash hududi aniqlanmadi (muassasa nomida tuman yo'q, PINFL hudud kodi noma'lum)</t>
-        </is>
-      </c>
-      <c r="G28" s="17" t="inlineStr"/>
+          <t>• [Past] Bir xil telefon raqami: Quysinova Rohshona To'lqin qizi, Xolmamatova Shoxista Sobir qizi, Zayidova Shaboda Sodiqovna
+• [Past] Bir xil telefon raqami: Quysinova Rohshona To'lqin qizi, Xolmamatova Shoxista Sobir qizi, Zayidova Shaboda Sodiqovna</t>
+        </is>
+      </c>
+      <c r="G28" s="17" t="inlineStr">
+        <is>
+          <t>Ha</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="17" t="n">
@@ -4646,12 +4153,12 @@
       </c>
       <c r="C29" s="17" t="inlineStr">
         <is>
-          <t>26-04</t>
+          <t>26-05</t>
         </is>
       </c>
       <c r="D29" s="17" t="inlineStr">
         <is>
-          <t>Ulugbekova Zara Ulug'bek qizi</t>
+          <t>Ne'matova Sevinch Hikmatullo qizi</t>
         </is>
       </c>
       <c r="E29" s="17" t="n">
@@ -4679,12 +4186,12 @@
       </c>
       <c r="C30" s="17" t="inlineStr">
         <is>
-          <t>26-04</t>
+          <t>26-05</t>
         </is>
       </c>
       <c r="D30" s="17" t="inlineStr">
         <is>
-          <t>Xujamuratova Durdona Bahrom qizi</t>
+          <t>Tursunova Fotima Qosim qizi</t>
         </is>
       </c>
       <c r="E30" s="17" t="n">
@@ -4692,7 +4199,7 @@
       </c>
       <c r="F30" s="17" t="inlineStr">
         <is>
-          <t>• [Past] Ma'lumotlar hali hujjat bilan tasdiqlanmagan</t>
+          <t>• [Past] Bir xil telefon raqami: Tursunov Sohibjon Hakim o'g'li, Tursunova Fotima Qosim qizi, Tursunova Zuhra Qosim qizi</t>
         </is>
       </c>
       <c r="G30" s="17" t="inlineStr">
@@ -4712,12 +4219,12 @@
       </c>
       <c r="C31" s="17" t="inlineStr">
         <is>
-          <t>26-04</t>
+          <t>26-05</t>
         </is>
       </c>
       <c r="D31" s="17" t="inlineStr">
         <is>
-          <t>Xurramova Shahnoza Shuhrat qizi</t>
+          <t>Tursunova Zuhra Qosim qizi</t>
         </is>
       </c>
       <c r="E31" s="17" t="n">
@@ -4725,10 +4232,14 @@
       </c>
       <c r="F31" s="17" t="inlineStr">
         <is>
-          <t>• [Past] Bir xil telefon raqami: Xurramova Shahnoza Shuhrat qizi, Xurramova Shahrizoda Shuhrat qizi</t>
-        </is>
-      </c>
-      <c r="G31" s="17" t="inlineStr"/>
+          <t>• [Past] Bir xil telefon raqami: Tursunov Sohibjon Hakim o'g'li, Tursunova Fotima Qosim qizi, Tursunova Zuhra Qosim qizi</t>
+        </is>
+      </c>
+      <c r="G31" s="17" t="inlineStr">
+        <is>
+          <t>Ha</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="17" t="n">
@@ -4741,20 +4252,21 @@
       </c>
       <c r="C32" s="17" t="inlineStr">
         <is>
-          <t>26-04</t>
+          <t>26-06</t>
         </is>
       </c>
       <c r="D32" s="17" t="inlineStr">
         <is>
-          <t>Xurramova Shahrizoda Shuhrat qizi</t>
+          <t>Niyozova Sevara Turoqulovna</t>
         </is>
       </c>
       <c r="E32" s="17" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F32" s="17" t="inlineStr">
         <is>
-          <t>• [Past] Bir xil telefon raqami: Xurramova Shahnoza Shuhrat qizi, Xurramova Shahrizoda Shuhrat qizi</t>
+          <t>• [Past] JSHSHIR ichida bo'shliq / ortiqcha belgi bor
+• [Past] Ma'lumotlar hali hujjat bilan tasdiqlanmagan</t>
         </is>
       </c>
       <c r="G32" s="17" t="inlineStr">
@@ -4774,294 +4286,32 @@
       </c>
       <c r="C33" s="17" t="inlineStr">
         <is>
-          <t>26-04</t>
+          <t>26-06</t>
         </is>
       </c>
       <c r="D33" s="17" t="inlineStr">
         <is>
-          <t>Zayidova Shaboda Sodiqovna</t>
+          <t>Uzoqova Fazilat Nurali qizi</t>
         </is>
       </c>
       <c r="E33" s="17" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F33" s="17" t="inlineStr">
-        <is>
-          <t>• [Past] Bir xil telefon raqami: Quysinova Rohshona To'lqin qizi, Xolmamatova Shoxista Sobir qizi, Zayidova Shaboda Sodiqovna
-• [Past] Bir xil telefon raqami: Quysinova Rohshona To'lqin qizi, Xolmamatova Shoxista Sobir qizi, Zayidova Shaboda Sodiqovna</t>
-        </is>
-      </c>
-      <c r="G33" s="17" t="inlineStr">
-        <is>
-          <t>Ha</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="17" t="n">
-        <v>33</v>
-      </c>
-      <c r="B34" s="19" t="inlineStr">
-        <is>
-          <t>Past</t>
-        </is>
-      </c>
-      <c r="C34" s="17" t="inlineStr">
-        <is>
-          <t>26-05</t>
-        </is>
-      </c>
-      <c r="D34" s="17" t="inlineStr">
-        <is>
-          <t>Jurayeva Madina Odil qizi</t>
-        </is>
-      </c>
-      <c r="E34" s="17" t="n">
-        <v>1</v>
-      </c>
-      <c r="F34" s="17" t="inlineStr">
-        <is>
-          <t>• [Past] Yashash hududi aniqlanmadi (muassasa nomida tuman yo'q, PINFL hudud kodi noma'lum)</t>
-        </is>
-      </c>
-      <c r="G34" s="17" t="inlineStr">
-        <is>
-          <t>Ha</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="17" t="n">
-        <v>34</v>
-      </c>
-      <c r="B35" s="19" t="inlineStr">
-        <is>
-          <t>Past</t>
-        </is>
-      </c>
-      <c r="C35" s="17" t="inlineStr">
-        <is>
-          <t>26-05</t>
-        </is>
-      </c>
-      <c r="D35" s="17" t="inlineStr">
-        <is>
-          <t>Ne'matova Sevinch Hikmatullo qizi</t>
-        </is>
-      </c>
-      <c r="E35" s="17" t="n">
-        <v>1</v>
-      </c>
-      <c r="F35" s="17" t="inlineStr">
-        <is>
-          <t>• [Past] Ma'lumotlar hali hujjat bilan tasdiqlanmagan</t>
-        </is>
-      </c>
-      <c r="G35" s="17" t="inlineStr">
-        <is>
-          <t>Ha</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="17" t="n">
-        <v>35</v>
-      </c>
-      <c r="B36" s="19" t="inlineStr">
-        <is>
-          <t>Past</t>
-        </is>
-      </c>
-      <c r="C36" s="17" t="inlineStr">
-        <is>
-          <t>26-05</t>
-        </is>
-      </c>
-      <c r="D36" s="17" t="inlineStr">
-        <is>
-          <t>Tursunova Fotima Qosim qizi</t>
-        </is>
-      </c>
-      <c r="E36" s="17" t="n">
-        <v>1</v>
-      </c>
-      <c r="F36" s="17" t="inlineStr">
-        <is>
-          <t>• [Past] Bir xil telefon raqami: Tursunov Sohibjon Hakim o'g'li, Tursunova Fotima Qosim qizi, Tursunova Zuhra Qosim qizi</t>
-        </is>
-      </c>
-      <c r="G36" s="17" t="inlineStr">
-        <is>
-          <t>Ha</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="17" t="n">
-        <v>36</v>
-      </c>
-      <c r="B37" s="19" t="inlineStr">
-        <is>
-          <t>Past</t>
-        </is>
-      </c>
-      <c r="C37" s="17" t="inlineStr">
-        <is>
-          <t>26-05</t>
-        </is>
-      </c>
-      <c r="D37" s="17" t="inlineStr">
-        <is>
-          <t>Tursunova Zuhra Qosim qizi</t>
-        </is>
-      </c>
-      <c r="E37" s="17" t="n">
-        <v>1</v>
-      </c>
-      <c r="F37" s="17" t="inlineStr">
-        <is>
-          <t>• [Past] Bir xil telefon raqami: Tursunov Sohibjon Hakim o'g'li, Tursunova Fotima Qosim qizi, Tursunova Zuhra Qosim qizi</t>
-        </is>
-      </c>
-      <c r="G37" s="17" t="inlineStr">
-        <is>
-          <t>Ha</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="17" t="n">
-        <v>37</v>
-      </c>
-      <c r="B38" s="19" t="inlineStr">
-        <is>
-          <t>Past</t>
-        </is>
-      </c>
-      <c r="C38" s="17" t="inlineStr">
-        <is>
-          <t>26-06</t>
-        </is>
-      </c>
-      <c r="D38" s="17" t="inlineStr">
-        <is>
-          <t>Eshimova Zilola Bekzod qizi</t>
-        </is>
-      </c>
-      <c r="E38" s="17" t="n">
-        <v>1</v>
-      </c>
-      <c r="F38" s="17" t="inlineStr">
-        <is>
-          <t>• [Past] Yashash hududi aniqlanmadi (muassasa nomida tuman yo'q, PINFL hudud kodi noma'lum)</t>
-        </is>
-      </c>
-      <c r="G38" s="17" t="inlineStr">
-        <is>
-          <t>Ha</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="17" t="n">
-        <v>38</v>
-      </c>
-      <c r="B39" s="19" t="inlineStr">
-        <is>
-          <t>Past</t>
-        </is>
-      </c>
-      <c r="C39" s="17" t="inlineStr">
-        <is>
-          <t>26-06</t>
-        </is>
-      </c>
-      <c r="D39" s="17" t="inlineStr">
-        <is>
-          <t>Niyozova Sevara Turoqulovna</t>
-        </is>
-      </c>
-      <c r="E39" s="17" t="n">
-        <v>2</v>
-      </c>
-      <c r="F39" s="17" t="inlineStr">
-        <is>
-          <t>• [Past] JSHSHIR ichida bo'shliq / ortiqcha belgi bor
-• [Past] Ma'lumotlar hali hujjat bilan tasdiqlanmagan</t>
-        </is>
-      </c>
-      <c r="G39" s="17" t="inlineStr">
-        <is>
-          <t>Ha</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="17" t="n">
-        <v>39</v>
-      </c>
-      <c r="B40" s="19" t="inlineStr">
-        <is>
-          <t>Past</t>
-        </is>
-      </c>
-      <c r="C40" s="17" t="inlineStr">
-        <is>
-          <t>26-06</t>
-        </is>
-      </c>
-      <c r="D40" s="17" t="inlineStr">
-        <is>
-          <t>Sayfillayeva Shodiyona Sayfilla qizi</t>
-        </is>
-      </c>
-      <c r="E40" s="17" t="n">
-        <v>1</v>
-      </c>
-      <c r="F40" s="17" t="inlineStr">
-        <is>
-          <t>• [Past] Yashash hududi aniqlanmadi (muassasa nomida tuman yo'q, PINFL hudud kodi noma'lum)</t>
-        </is>
-      </c>
-      <c r="G40" s="17" t="inlineStr"/>
-    </row>
-    <row r="41">
-      <c r="A41" s="17" t="n">
-        <v>40</v>
-      </c>
-      <c r="B41" s="19" t="inlineStr">
-        <is>
-          <t>Past</t>
-        </is>
-      </c>
-      <c r="C41" s="17" t="inlineStr">
-        <is>
-          <t>26-06</t>
-        </is>
-      </c>
-      <c r="D41" s="17" t="inlineStr">
-        <is>
-          <t>Uzoqova Fazilat Nurali qizi</t>
-        </is>
-      </c>
-      <c r="E41" s="17" t="n">
-        <v>3</v>
-      </c>
-      <c r="F41" s="17" t="inlineStr">
         <is>
           <t>• [Past] JSHSHIR ichida bo'shliq / ortiqcha belgi bor
 • [Past] Pasport raqamida bo'shliq / kichik harf bor
 • [Past] Ma'lumotlar hali hujjat bilan tasdiqlanmagan</t>
         </is>
       </c>
-      <c r="G41" s="17" t="inlineStr">
+      <c r="G33" s="17" t="inlineStr">
         <is>
           <t>Ha</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G41"/>
+  <autoFilter ref="A1:G33"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -6347,11 +5597,7 @@
           <t>917090876</t>
         </is>
       </c>
-      <c r="G45" s="17" t="inlineStr">
-        <is>
-          <t>Ha</t>
-        </is>
-      </c>
+      <c r="G45" s="17" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" s="17" t="n">
@@ -6378,11 +5624,7 @@
           <t>997307709</t>
         </is>
       </c>
-      <c r="G46" s="17" t="inlineStr">
-        <is>
-          <t>Ha</t>
-        </is>
-      </c>
+      <c r="G46" s="17" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" s="17" t="n">
@@ -7152,11 +6394,7 @@
           <t>885020703 / 880037679</t>
         </is>
       </c>
-      <c r="G72" s="17" t="inlineStr">
-        <is>
-          <t>Ha</t>
-        </is>
-      </c>
+      <c r="G72" s="17" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" s="17" t="n">
@@ -7582,11 +6820,7 @@
           <t>997422473</t>
         </is>
       </c>
-      <c r="G86" s="17" t="inlineStr">
-        <is>
-          <t>Ha</t>
-        </is>
-      </c>
+      <c r="G86" s="17" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" s="17" t="n">
@@ -8722,11 +7956,7 @@
           <t>946034407 / 912138081</t>
         </is>
       </c>
-      <c r="G126" s="17" t="inlineStr">
-        <is>
-          <t>Ha</t>
-        </is>
-      </c>
+      <c r="G126" s="17" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" s="17" t="n">
@@ -9399,11 +8629,7 @@
           <t>919490481</t>
         </is>
       </c>
-      <c r="G149" s="17" t="inlineStr">
-        <is>
-          <t>Ha</t>
-        </is>
-      </c>
+      <c r="G149" s="17" t="inlineStr"/>
     </row>
     <row r="150">
       <c r="A150" s="17" t="n">
@@ -15075,7 +14301,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F2"/>
+  <dimension ref="A1:F3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -15148,8 +14374,34 @@
         </is>
       </c>
     </row>
+    <row r="3">
+      <c r="A3" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" s="17" t="inlineStr">
+        <is>
+          <t>26-03</t>
+        </is>
+      </c>
+      <c r="C3" s="17" t="inlineStr">
+        <is>
+          <t>Xurramova Sabina Yuldosh qizi</t>
+        </is>
+      </c>
+      <c r="D3" s="17" t="inlineStr">
+        <is>
+          <t>60803048230011</t>
+        </is>
+      </c>
+      <c r="E3" s="17" t="inlineStr">
+        <is>
+          <t>Yakkabog' tumanidan (foydalanuvchi tasdiqladi, 26.09.2026); JSHSHIR hudud kodi 823 noma'lum</t>
+        </is>
+      </c>
+      <c r="F3" s="17" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:F2"/>
+  <autoFilter ref="A1:F3"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>